--- a/tests/realSuite/Piano-Viaggi-Corsa-Campestre_IS_12-marzo-25_con-cel-3/input_corretto.xlsx
+++ b/tests/realSuite/Piano-Viaggi-Corsa-Campestre_IS_12-marzo-25_con-cel-3/input_corretto.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Istituto di istruzione superiore "Alcide Degasperi", Sagrato della Chiesa, Borgo Valsugana, Comunità Valsugana e Tesino, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38051, Italia</t>
+          <t>Via XXIV Maggio, 7, Via Ventiquattro Maggio, Borgo Valsugana, Comunità Valsugana e Tesino, Provincia di Trento, Trentino – Alto Adige/Südtirol, 38051, Italy</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -608,7 +608,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Liceo Maffei, Viale Damiano Chiesa, Alboletta, Sant'Alessandro, Riva del Garda, Comunità Alto Garda e Ledro, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38066, Italia</t>
+          <t>5, Viale Francesca Alberti Lutti, Alboletta, Sant'Alessandro, Riva del Garda, Comunità Alto Garda e Ledro, Provincia di Trento, Trentino – Alto Adige/Südtirol, 38066, Italy</t>
         </is>
       </c>
       <c r="C11" t="n">
